--- a/output/pdf_financials_xlsx/LFST.xlsx
+++ b/output/pdf_financials_xlsx/LFST.xlsx
@@ -2765,22 +2765,22 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>19.085412</v>
+        <v>39.199938</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>19.262133</v>
+        <v>24.320901</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>24.39872</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.785301</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>55.018894</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>55.083188</v>
       </c>
     </row>
     <row r="93">
@@ -4640,7 +4640,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -5538,7 +5542,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
         <v>20.114526</v>
       </c>

--- a/output/pdf_financials_xlsx/LFST.xlsx
+++ b/output/pdf_financials_xlsx/LFST.xlsx
@@ -661,10 +661,10 @@
         <v>17.901102</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>4.638654</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>2.455665</v>
       </c>
     </row>
     <row r="11">
@@ -686,10 +686,10 @@
         <v>-12.556817</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.20475</v>
+        <v>-4.433904</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.058989</v>
+        <v>-2.396676</v>
       </c>
     </row>
     <row r="12">
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.040733</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.049508</v>
       </c>
     </row>
     <row r="13">
@@ -1146,10 +1146,10 @@
         <v>-14.122517</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.445558</v>
+        <v>-1.486291</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.98989</v>
+        <v>-3.039398</v>
       </c>
     </row>
     <row r="28">
@@ -1196,10 +1196,10 @@
         <v>-13.815698</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.419379</v>
+        <v>-1.460112</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.982481</v>
+        <v>-3.031989</v>
       </c>
     </row>
     <row r="30">
@@ -1221,10 +1221,10 @@
         <v>-63.78486597105971</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-241.0621906854936</v>
+        <v>-247.9801359370383</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-1196.020724474369</v>
+        <v>-1215.874193457835</v>
       </c>
     </row>
     <row r="31">
@@ -3553,10 +3553,10 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.307215</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.192401</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
@@ -3578,10 +3578,10 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.307215</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.192401</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -11742,7 +11742,11 @@
           <t>Lease payments 15</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -14428,7 +14432,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -14452,10 +14456,10 @@
         </is>
       </c>
       <c r="I236" s="5" t="n">
-        <v>-4.638654</v>
+        <v>4.638654</v>
       </c>
       <c r="J236" s="5" t="n">
-        <v>-2.455665</v>
+        <v>2.455665</v>
       </c>
     </row>
     <row r="237">
@@ -14556,7 +14560,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -14600,7 +14604,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">

--- a/output/pdf_financials_xlsx/LFST.xlsx
+++ b/output/pdf_financials_xlsx/LFST.xlsx
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.00176</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.13144</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -12840,7 +12840,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E200" s="5" t="n">
         <v>0.00176</v>
       </c>

--- a/output/pdf_financials_xlsx/LFST.xlsx
+++ b/output/pdf_financials_xlsx/LFST.xlsx
@@ -508,7 +508,7 @@
         <v>22.068682</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>21.659837</v>
+        <v>1.364978</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0.588802</v>
@@ -533,7 +533,7 @@
         <v>16.186263</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>15.019108</v>
+        <v>0.599361</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0.384052</v>
@@ -558,7 +558,7 @@
         <v>4.95982</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5.344285</v>
+        <v>0.763364</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0.20475</v>
@@ -658,7 +658,7 @@
         <v>20.081217</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>17.901102</v>
+        <v>6.95079</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>4.638654</v>
@@ -683,7 +683,7 @@
         <v>-15.121397</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-12.556817</v>
+        <v>-6.187426</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>-4.433904</v>
@@ -783,7 +783,7 @@
         <v>3.904639</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1.014732</v>
+        <v>-0.153134</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>-4.463481</v>
@@ -802,16 +802,16 @@
         <v>-52.609578</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-47.436712</v>
+        <v>-23.963872</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-18.920248</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-14.122517</v>
+        <v>-6.042625</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-1.445558</v>
+        <v>-4.053657</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-2.98989</v>
@@ -827,16 +827,16 @@
         <v>26.180118</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>23.635963</v>
+        <v>0.163123</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0.224253</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.003153</v>
+        <v>-0.025452</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>2.608099</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -925,17 +925,21 @@
       <c r="B20" s="3" t="n">
         <v>-26.42946</v>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>-1.570061</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>3.260496</v>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E20" s="3" t="n">
         <v>-14.12567</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-1.445558</v>
+        <v>-4.053657</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-2.98989</v>
@@ -951,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-1.570061</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>3.260496</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -1137,16 +1141,16 @@
         <v>-52.609578</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-47.436712</v>
+        <v>-23.963872</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-18.920248</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-14.122517</v>
+        <v>-6.042625</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.486291</v>
+        <v>-4.09439</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-3.039398</v>
@@ -1168,7 +1172,7 @@
         <v>0.403723</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.306819</v>
+        <v>0.056542</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0.026179</v>
@@ -1187,16 +1191,16 @@
         <v>-50.423145</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-45.71711</v>
+        <v>-22.24427</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-18.516525</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-13.815698</v>
+        <v>-5.986083</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.460112</v>
+        <v>-4.068211</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-3.031989</v>
@@ -1212,16 +1216,16 @@
         <v>-200.8531504114225</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-216.1994510210844</v>
+        <v>-105.1947282399254</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-83.90408181150102</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-63.78486597105971</v>
+        <v>-438.5479472929234</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-247.9801359370383</v>
+        <v>-690.9302278185196</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-1215.874193457835</v>
@@ -1237,16 +1241,16 @@
         <v>-49.76302604061944</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-49.82630963124088</v>
+        <v>-0.680703852866515</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-1.185254019926166</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.02232604853653212</v>
+        <v>-0.4212076705074367</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-64.33941006848877</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -1268,7 +1272,7 @@
         <v>-69.94300339277171</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-65.21595707299183</v>
+        <v>-1034.864298179165</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>-245.5083372678761</v>
@@ -1441,22 +1445,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.613767</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.529863</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>1.707292</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.097691</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.003249</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.01286</v>
       </c>
     </row>
     <row r="41">
@@ -1466,22 +1470,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>5.679536</v>
+        <v>6.293303</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>4.369977</v>
+        <v>4.89984</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>5.805832</v>
+        <v>7.513124</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2.33184</v>
+        <v>2.429531</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1.155085</v>
+        <v>1.158334</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.668892</v>
+        <v>0.681752</v>
       </c>
     </row>
     <row r="42">
@@ -1641,22 +1645,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.081725</v>
+        <v>1.467958</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.117118</v>
+        <v>4.587255</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.914426</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.484005</v>
+        <v>0.386314</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.047721</v>
+        <v>0.044472</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.068412</v>
+        <v>0.055552</v>
       </c>
     </row>
     <row r="49">
@@ -2128,22 +2132,22 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>6.235976</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>6.579907</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>3.975768</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.869456</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.348041</v>
       </c>
     </row>
     <row r="68">
@@ -2931,10 +2935,10 @@
         <v>-15.435499</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-14.12567</v>
+        <v>-6.017173</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-1.445558</v>
+        <v>-4.053657</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-2.98989</v>
@@ -3156,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
@@ -3863,7 +3867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J337"/>
+  <dimension ref="A1:J362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7544,7 +7548,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -11200,7 +11208,11 @@
           <t>Impairment loss on goodwill 11</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -14858,7 +14870,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -15790,10 +15806,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario</t>
+        </is>
+      </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Notes November 30, 2023 November</t>
+          <t>March</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -15807,16 +15827,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G267" s="5" t="n">
-        <v>0.002022</v>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H267" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002025</v>
+      </c>
+      <c r="I267" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -15830,29 +15850,37 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr"/>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario</t>
+        </is>
+      </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Gross revenue $</t>
+          <t>Notes November 30, 2024 November</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
-      <c r="E268" s="5" t="n">
-        <v>27.108545</v>
-      </c>
-      <c r="F268" s="5" t="n">
-        <v>25.682426</v>
-      </c>
-      <c r="G268" s="5" t="n">
-        <v>28.517472</v>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H268" s="5" t="n">
-        <v>27.613705</v>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="I268" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -15866,33 +15894,41 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr"/>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario</t>
+        </is>
+      </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Excise taxes</t>
+          <t>Revenue 5,17 $</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>ExciseTaxes</t>
-        </is>
-      </c>
-      <c r="E269" s="5" t="n">
-        <v>-2.004062</v>
-      </c>
-      <c r="F269" s="5" t="n">
-        <v>-4.536623</v>
-      </c>
-      <c r="G269" s="5" t="n">
-        <v>-6.44879</v>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H269" s="5" t="n">
-        <v>-5.953868</v>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.364978</v>
+      </c>
+      <c r="I269" s="5" t="n">
+        <v>0.588802</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -15906,15 +15942,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario</t>
+        </is>
+      </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Net revenue 5,17</t>
+          <t>Cost of goods sold</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -15927,16 +15967,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G270" s="5" t="n">
-        <v>22.068682</v>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H270" s="5" t="n">
-        <v>21.659837</v>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.599361</v>
+      </c>
+      <c r="I270" s="5" t="n">
+        <v>0.168493</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
@@ -15950,17 +15990,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr"/>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario</t>
+        </is>
+      </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Cost of goods sold 7, 27</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>Gross profit before inventory adjustment</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -15971,16 +16011,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G271" s="5" t="n">
-        <v>16.186263</v>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H271" s="5" t="n">
-        <v>15.019108</v>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.765617</v>
+      </c>
+      <c r="I271" s="5" t="n">
+        <v>0.420309</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -15994,29 +16034,37 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr"/>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario</t>
+        </is>
+      </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Gross profit before inventory adjustment</t>
+          <t>Inventory write-down 7</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
-      <c r="E272" s="5" t="n">
-        <v>2.089691</v>
-      </c>
-      <c r="F272" s="5" t="n">
-        <v>1.971741</v>
-      </c>
-      <c r="G272" s="5" t="n">
-        <v>5.882419</v>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H272" s="5" t="n">
-        <v>6.640729</v>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002253</v>
+      </c>
+      <c r="I272" s="5" t="n">
+        <v>0.215559</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
@@ -16030,13 +16078,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr"/>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario</t>
+        </is>
+      </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Inventory (write-down) 7</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -16047,16 +16103,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G273" s="5" t="n">
-        <v>-0.9225989999999999</v>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H273" s="5" t="n">
-        <v>-1.296444</v>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.763364</v>
+      </c>
+      <c r="I273" s="5" t="n">
+        <v>0.20475</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -16072,7 +16128,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -16091,16 +16147,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G274" s="5" t="n">
-        <v>7.540457</v>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H274" s="5" t="n">
-        <v>6.699299</v>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.368374</v>
+      </c>
+      <c r="I274" s="5" t="n">
+        <v>1.693908</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -16116,12 +16172,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Office and general expenses 27</t>
+          <t>Office and general expenses</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -16135,16 +16191,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G275" s="5" t="n">
-        <v>4.556743</v>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H275" s="5" t="n">
-        <v>3.538041</v>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.383309</v>
+      </c>
+      <c r="I275" s="5" t="n">
+        <v>1.434873</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -16160,15 +16216,19 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Technological development</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -16179,16 +16239,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G276" s="5" t="n">
-        <v>0.130053</v>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H276" s="5" t="n">
-        <v>0.018745</v>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.126657</v>
+      </c>
+      <c r="I276" s="5" t="n">
+        <v>0.581124</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -16204,12 +16264,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Selling and marketing expense 27</t>
+          <t>Selling and marketing expense</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -16227,16 +16287,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G277" s="5" t="n">
-        <v>5.3617</v>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H277" s="5" t="n">
-        <v>5.252051</v>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.13111</v>
+      </c>
+      <c r="I277" s="5" t="n">
+        <v>0.479118</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -16252,17 +16312,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Depreciation and amortization 9</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -16275,16 +16335,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G278" s="5" t="n">
-        <v>1.332582</v>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H278" s="5" t="n">
-        <v>1.20135</v>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.056542</v>
+      </c>
+      <c r="I278" s="5" t="n">
+        <v>0.026179</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -16300,19 +16360,15 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 9, 10, 27</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Share-based compensation 16 (d)(e), 22</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -16323,16 +16379,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G279" s="5" t="n">
-        <v>0.403723</v>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H279" s="5" t="n">
-        <v>0.306819</v>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.884798</v>
+      </c>
+      <c r="I279" s="5" t="n">
+        <v>0.423452</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -16348,15 +16404,19 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Share-based compensation 16 (b)(d)(e)</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -16367,16 +16427,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G280" s="5" t="n">
-        <v>0.755959</v>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H280" s="5" t="n">
-        <v>0.884798</v>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.95079</v>
+      </c>
+      <c r="I280" s="5" t="n">
+        <v>4.638654</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
@@ -16392,19 +16452,15 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Total Operating expenses</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Restructuring and other costs</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -16415,11 +16471,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G281" s="5" t="n">
-        <v>20.081217</v>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H281" s="5" t="n">
-        <v>17.901102</v>
+        <v>0.008333</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -16440,12 +16498,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Restructuring and other costs</t>
+          <t>Loss before following:</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -16459,16 +16517,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G282" s="5" t="n">
-        <v>0.078333</v>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H282" s="5" t="n">
-        <v>0.083333</v>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.195759</v>
+      </c>
+      <c r="I282" s="5" t="n">
+        <v>-4.433904</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
@@ -16484,15 +16542,19 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Loss before following:</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
+          <t>Other (income) 18</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -16503,16 +16565,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G283" s="5" t="n">
-        <v>-15.19973</v>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H283" s="5" t="n">
-        <v>-12.640151</v>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.162742</v>
+      </c>
+      <c r="I283" s="5" t="n">
+        <v>-0.409824</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -16528,12 +16590,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Other (income) expenses 18</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -16551,16 +16613,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G284" s="5" t="n">
-        <v>0.198791</v>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H284" s="5" t="n">
-        <v>-0.470504</v>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.009608</v>
+      </c>
+      <c r="I284" s="5" t="n">
+        <v>0.029577</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
@@ -16576,15 +16638,19 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Earn-out shares issued 16 (b)</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
+          <t>Loss before income tax</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -16595,18 +16661,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G285" s="5" t="n">
-        <v>1.036397</v>
-      </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H285" s="5" t="n">
+        <v>-6.042625</v>
+      </c>
+      <c r="I285" s="5" t="n">
+        <v>-4.053657</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -16622,15 +16686,19 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Impairment loss on assets 9, 10</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr"/>
+          <t>Income tax recovery</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -16641,11 +16709,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G286" s="5" t="n">
-        <v>2.5</v>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H286" s="5" t="n">
-        <v>1.7</v>
+        <v>0.025452</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -16666,12 +16736,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Impairment loss on goodwill 11</t>
+          <t>Net (loss) from continuing operations, net of tax</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -16691,12 +16761,10 @@
         </is>
       </c>
       <c r="H287" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.017173</v>
+      </c>
+      <c r="I287" s="5" t="n">
+        <v>-4.053657</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
@@ -16712,19 +16780,15 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Gain (loss) from discontinued operations, net of tax 4</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -16735,16 +16799,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G288" s="5" t="n">
-        <v>-0.01467</v>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H288" s="5" t="n">
-        <v>0.00287</v>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.108497</v>
+      </c>
+      <c r="I288" s="5" t="n">
+        <v>2.608099</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -16760,19 +16824,15 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Total other (income) expenses</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Net (loss), net of tax $</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -16783,16 +16843,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G289" s="5" t="n">
-        <v>3.720518</v>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H289" s="5" t="n">
-        <v>1.482366</v>
-      </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-14.12567</v>
+      </c>
+      <c r="I289" s="5" t="n">
+        <v>-1.445558</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -16808,19 +16868,15 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Loss before income tax</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Net loss per share (basic and diluted) from continuing operations $</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -16831,16 +16887,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G290" s="5" t="n">
-        <v>-18.920248</v>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H290" s="5" t="n">
-        <v>-14.122517</v>
-      </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.47e-07</v>
+      </c>
+      <c r="I290" s="5" t="n">
+        <v>-1.28e-07</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -16856,19 +16912,15 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Mississauga, Ontario</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Income tax (expense) recovery 19 (a)</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Net loss per share (basic and diluted) from discontinued operations $</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -16879,16 +16931,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G291" s="5" t="n">
-        <v>0.224253</v>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H291" s="5" t="n">
-        <v>-0.003153</v>
-      </c>
-      <c r="I291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.32e-07</v>
+      </c>
+      <c r="I291" s="5" t="n">
+        <v>8.200000000000001e-08</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -16904,35 +16956,29 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Weighted average number of outstanding</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Net loss from continuing operations, net of tax</t>
+          <t>Weighted average number of outstanding common shares (basic and diluted)</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E292" s="5" t="n">
+        <v>323.953663</v>
+      </c>
+      <c r="F292" s="5" t="n">
+        <v>390.076063</v>
       </c>
       <c r="G292" s="5" t="n">
-        <v>-18.695995</v>
+        <v>416.362028</v>
       </c>
       <c r="H292" s="5" t="n">
-        <v>-14.12567</v>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>24.392842</v>
+      </c>
+      <c r="I292" s="5" t="n">
+        <v>31.783495</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
@@ -16946,14 +16992,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Gain on sale of discontinued operations 4</t>
+          <t>Notes November 30, 2023 November</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -16968,12 +17010,10 @@
         </is>
       </c>
       <c r="G293" s="5" t="n">
-        <v>4.096558</v>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002022</v>
+      </c>
+      <c r="H293" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
@@ -16992,34 +17032,24 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
-          <t>(Loss) from discontinued operations 4</t>
+          <t>Gross revenue $</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E294" s="5" t="n">
+        <v>27.108545</v>
+      </c>
+      <c r="F294" s="5" t="n">
+        <v>25.682426</v>
       </c>
       <c r="G294" s="5" t="n">
-        <v>-0.836062</v>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>28.517472</v>
+      </c>
+      <c r="H294" s="5" t="n">
+        <v>27.613705</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
@@ -17038,38 +17068,28 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Net income (loss) from discontinued operations</t>
+          <t>Excise taxes</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ExciseTaxes</t>
+        </is>
+      </c>
+      <c r="E295" s="5" t="n">
+        <v>-2.004062</v>
+      </c>
+      <c r="F295" s="5" t="n">
+        <v>-4.536623</v>
       </c>
       <c r="G295" s="5" t="n">
-        <v>3.260496</v>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.44879</v>
+      </c>
+      <c r="H295" s="5" t="n">
+        <v>-5.953868</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
@@ -17088,19 +17108,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Net loss $</t>
+          <t>Net revenue 5,17</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -17114,10 +17130,10 @@
         </is>
       </c>
       <c r="G296" s="5" t="n">
-        <v>-15.435499</v>
+        <v>22.068682</v>
       </c>
       <c r="H296" s="5" t="n">
-        <v>-14.12567</v>
+        <v>21.659837</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
@@ -17136,17 +17152,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Net loss per share (basic and diluted) from continuing operations $</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>Cost of goods sold 7, 27</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -17158,10 +17174,10 @@
         </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>-4e-08</v>
+        <v>16.186263</v>
       </c>
       <c r="H297" s="5" t="n">
-        <v>-3e-08</v>
+        <v>15.019108</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
@@ -17180,34 +17196,24 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Net income per share (basic and diluted) from discontinued $</t>
+          <t>Gross profit before inventory adjustment</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E298" s="5" t="n">
+        <v>2.089691</v>
+      </c>
+      <c r="F298" s="5" t="n">
+        <v>1.971741</v>
       </c>
       <c r="G298" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.882419</v>
+      </c>
+      <c r="H298" s="5" t="n">
+        <v>6.640729</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
@@ -17226,28 +17232,28 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Weighted average number of outstanding</t>
-        </is>
-      </c>
+      <c r="B299" t="inlineStr"/>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Weighted average number of outstanding common shares (basic and diluted)</t>
+          <t>Inventory (write-down) 7</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
-      <c r="E299" s="5" t="n">
-        <v>323.953663</v>
-      </c>
-      <c r="F299" s="5" t="n">
-        <v>390.076063</v>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G299" s="5" t="n">
-        <v>416.362028</v>
+        <v>-0.9225989999999999</v>
       </c>
       <c r="H299" s="5" t="n">
-        <v>487.856845</v>
+        <v>-1.296444</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
@@ -17266,32 +17272,32 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr"/>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Net revenue 5,19</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Salaries and other compensation costs 22</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F300" s="5" t="n">
-        <v>21.145803</v>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G300" s="5" t="n">
-        <v>22.068682</v>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.540457</v>
+      </c>
+      <c r="H300" s="5" t="n">
+        <v>6.699299</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
@@ -17310,10 +17316,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr"/>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Inventory write-down 7</t>
+          <t>Office and general expenses 27</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -17322,16 +17332,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F301" s="5" t="n">
-        <v>-1.85145</v>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G301" s="5" t="n">
-        <v>-0.9225989999999999</v>
-      </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.556743</v>
+      </c>
+      <c r="H301" s="5" t="n">
+        <v>3.538041</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
@@ -17350,26 +17360,32 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr"/>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Salaries and other compensation costs</t>
+          <t>Technological development</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
-      <c r="E302" s="5" t="n">
-        <v>10.534248</v>
-      </c>
-      <c r="F302" s="5" t="n">
-        <v>10.246141</v>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G302" s="5" t="n">
-        <v>7.540457</v>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.130053</v>
+      </c>
+      <c r="H302" s="5" t="n">
+        <v>0.018745</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
@@ -17388,26 +17404,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr"/>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Technological development</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
-      <c r="E303" s="5" t="n">
-        <v>1.689964</v>
-      </c>
-      <c r="F303" s="5" t="n">
-        <v>0.631399</v>
+          <t>Selling and marketing expense 27</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>SellingAndMarketingExpense</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G303" s="5" t="n">
-        <v>0.130053</v>
-      </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.3617</v>
+      </c>
+      <c r="H303" s="5" t="n">
+        <v>5.252051</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
@@ -17426,15 +17452,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr"/>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 10,11</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -17442,16 +17472,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F304" s="5" t="n">
-        <v>1.719602</v>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G304" s="5" t="n">
-        <v>1.474007</v>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.332582</v>
+      </c>
+      <c r="H304" s="5" t="n">
+        <v>1.20135</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
@@ -17470,28 +17500,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Share-based compensation 18 (d)(e)</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>Depreciation and amortization 9, 10, 27</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F305" s="5" t="n">
-        <v>1.263877</v>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G305" s="5" t="n">
-        <v>0.755959</v>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.403723</v>
+      </c>
+      <c r="H305" s="5" t="n">
+        <v>0.306819</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
@@ -17510,10 +17548,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Restructuring and other costs (recoveries) 16,20</t>
+          <t>Share-based compensation 16 (b)(d)(e)</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -17522,16 +17564,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F306" s="5" t="n">
-        <v>-0.113676</v>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G306" s="5" t="n">
-        <v>0.078333</v>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.755959</v>
+      </c>
+      <c r="H306" s="5" t="n">
+        <v>0.884798</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -17550,26 +17592,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr"/>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Loss before following:</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr"/>
-      <c r="E307" s="5" t="n">
-        <v>-24.497825</v>
-      </c>
-      <c r="F307" s="5" t="n">
-        <v>-23.649134</v>
+          <t>Total Operating expenses</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G307" s="5" t="n">
-        <v>-15.19973</v>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20.081217</v>
+      </c>
+      <c r="H307" s="5" t="n">
+        <v>17.901102</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
@@ -17588,32 +17640,32 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Other expense 21</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Restructuring and other costs</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F308" s="5" t="n">
-        <v>0.126299</v>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G308" s="5" t="n">
-        <v>0.198791</v>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.078333</v>
+      </c>
+      <c r="H308" s="5" t="n">
+        <v>0.083333</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
@@ -17632,10 +17684,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr"/>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Change in fair value of convertible loan receivable 6 (b), 8 (ii)</t>
+          <t>Loss before following:</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -17644,18 +17700,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F309" s="5" t="n">
-        <v>-1.842862</v>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G309" s="5" t="n">
+        <v>-15.19973</v>
+      </c>
+      <c r="H309" s="5" t="n">
+        <v>-12.640151</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
@@ -17674,13 +17728,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr"/>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Earn-out shares issued 18 (b)</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>Other (income) expenses 18</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -17692,12 +17754,10 @@
         </is>
       </c>
       <c r="G310" s="5" t="n">
-        <v>1.036397</v>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.198791</v>
+      </c>
+      <c r="H310" s="5" t="n">
+        <v>-0.470504</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
@@ -17716,10 +17776,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr"/>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Impairment loss on intangible assets 11</t>
+          <t>Earn-out shares issued 16 (b)</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -17734,7 +17798,7 @@
         </is>
       </c>
       <c r="G311" s="5" t="n">
-        <v>2.5</v>
+        <v>1.036397</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
@@ -17758,30 +17822,32 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr"/>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E312" s="5" t="n">
-        <v>1.136119</v>
-      </c>
-      <c r="F312" s="5" t="n">
-        <v>0.134994</v>
+          <t>Impairment loss on assets 9, 10</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G312" s="5" t="n">
-        <v>-0.01467</v>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.5</v>
+      </c>
+      <c r="H312" s="5" t="n">
+        <v>1.7</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
@@ -17800,10 +17866,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr"/>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Loss from continuing operations before income tax</t>
+          <t>Impairment loss on goodwill 11</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -17812,16 +17882,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F313" s="5" t="n">
-        <v>-22.067565</v>
-      </c>
-      <c r="G313" s="5" t="n">
-        <v>-18.920248</v>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H313" s="5" t="n">
+        <v>0.25</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
@@ -17840,28 +17912,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr"/>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense) 22 (a)</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F314" s="5" t="n">
-        <v>-0.163123</v>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G314" s="5" t="n">
-        <v>0.224253</v>
-      </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.01467</v>
+      </c>
+      <c r="H314" s="5" t="n">
+        <v>0.00287</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
@@ -17880,28 +17960,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr"/>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Net loss from continuing operations, net of tax</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>Total other (income) expenses</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F315" s="5" t="n">
-        <v>-22.230688</v>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G315" s="5" t="n">
-        <v>-18.695995</v>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.720518</v>
+      </c>
+      <c r="H315" s="5" t="n">
+        <v>1.482366</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -17920,13 +18008,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr"/>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Gain on sale of discontinued operations 4</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>Loss before income tax</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -17938,12 +18034,10 @@
         </is>
       </c>
       <c r="G316" s="5" t="n">
-        <v>4.096558</v>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-18.920248</v>
+      </c>
+      <c r="H316" s="5" t="n">
+        <v>-14.122517</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
@@ -17962,28 +18056,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr"/>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>(Loss) from discontinued operations 4</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>Income tax (expense) recovery 19 (a)</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F317" s="5" t="n">
-        <v>-1.570061</v>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G317" s="5" t="n">
-        <v>-0.836062</v>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.224253</v>
+      </c>
+      <c r="H317" s="5" t="n">
+        <v>-0.003153</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
@@ -18002,32 +18104,32 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr"/>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Net income (loss) from discontinued operations</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>NetIncomeContinuousOperations</t>
-        </is>
-      </c>
+          <t>Net loss from continuing operations, net of tax</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F318" s="5" t="n">
-        <v>-1.570061</v>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G318" s="5" t="n">
-        <v>3.260496</v>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-18.695995</v>
+      </c>
+      <c r="H318" s="5" t="n">
+        <v>-14.12567</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
@@ -18046,10 +18148,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr"/>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Net (loss) per share (basic and diluted) from continuing</t>
+          <t>Gain on sale of discontinued operations 4</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -18058,11 +18164,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F319" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G319" s="5" t="n">
-        <v>-4e-08</v>
+        <v>4.096558</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -18088,25 +18196,31 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Net income (loss) per share (basic and diluted) from</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
+          <t>(Loss) from discontinued operations 4</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F320" s="5" t="n">
-        <v>-4e-09</v>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G320" s="5" t="n">
-        <v>1e-08</v>
+        <v>-0.836062</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
@@ -18130,27 +18244,33 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr"/>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Net revenue 4,18</t>
+          <t>Net income (loss) from discontinued operations</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E321" s="5" t="n">
-        <v>25.104483</v>
-      </c>
-      <c r="F321" s="5" t="n">
-        <v>22.819561</v>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G321" s="5" t="n">
+        <v>3.260496</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
@@ -18174,32 +18294,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr"/>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Cost of goods sold 6</t>
+          <t>Net loss $</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E322" s="5" t="n">
-        <v>23.014792</v>
-      </c>
-      <c r="F322" s="5" t="n">
-        <v>19.286332</v>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G322" s="5" t="n">
+        <v>-15.435499</v>
+      </c>
+      <c r="H322" s="5" t="n">
+        <v>-14.12567</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
@@ -18218,28 +18342,32 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr"/>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Inventory write-down 6</t>
+          <t>Net loss per share (basic and diluted) from continuing operations $</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
-      <c r="E323" s="5" t="n">
-        <v>-0.6311330000000001</v>
-      </c>
-      <c r="F323" s="5" t="n">
-        <v>-1.85145</v>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="H323" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
@@ -18258,27 +18386,29 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr"/>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 9,10</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E324" s="5" t="n">
-        <v>2.186433</v>
-      </c>
-      <c r="F324" s="5" t="n">
-        <v>2.043818</v>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net income per share (basic and diluted) from discontinued $</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="n">
+        <v>1e-08</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -18305,20 +18435,24 @@
       <c r="B325" t="inlineStr"/>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Share-based compensation 17 (d)</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr"/>
-      <c r="E325" s="5" t="n">
-        <v>0.772212</v>
+          <t>Net revenue 5,19</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F325" s="5" t="n">
-        <v>1.263877</v>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>21.145803</v>
+      </c>
+      <c r="G325" s="5" t="n">
+        <v>22.068682</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
@@ -18345,20 +18479,20 @@
       <c r="B326" t="inlineStr"/>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Restructuring and other costs (recoveries) 15,19</t>
+          <t>Inventory write-down 7</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
-      <c r="E326" s="5" t="n">
-        <v>-1.701007</v>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F326" s="5" t="n">
-        <v>-0.113676</v>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.85145</v>
+      </c>
+      <c r="G326" s="5" t="n">
+        <v>-0.9225989999999999</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
@@ -18385,20 +18519,18 @@
       <c r="B327" t="inlineStr"/>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Other expense (income) 20</t>
+          <t>Salaries and other compensation costs</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
       <c r="E327" s="5" t="n">
-        <v>-1.122492</v>
+        <v>10.534248</v>
       </c>
       <c r="F327" s="5" t="n">
-        <v>0.126772</v>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.246141</v>
+      </c>
+      <c r="G327" s="5" t="n">
+        <v>7.540457</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
@@ -18425,22 +18557,18 @@
       <c r="B328" t="inlineStr"/>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Change in fair value of convertible loan receivable 22(ii)</t>
+          <t>Technological development</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E328" s="5" t="n">
+        <v>1.689964</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>-1.842862</v>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.631399</v>
+      </c>
+      <c r="G328" s="5" t="n">
+        <v>0.130053</v>
       </c>
       <c r="H328" t="inlineStr">
         <is>
@@ -18467,22 +18595,24 @@
       <c r="B329" t="inlineStr"/>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Impairment on investment in associates 7</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
-      <c r="E329" s="5" t="n">
-        <v>1.016127</v>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depreciation and amortization 10,11</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F329" s="5" t="n">
+        <v>1.719602</v>
+      </c>
+      <c r="G329" s="5" t="n">
+        <v>1.474007</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
@@ -18509,22 +18639,20 @@
       <c r="B330" t="inlineStr"/>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Impairment loss on loans receivable</t>
+          <t>Share-based compensation 18 (d)(e)</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
-      <c r="E330" s="5" t="n">
-        <v>0.322887</v>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F330" s="5" t="n">
+        <v>1.263877</v>
+      </c>
+      <c r="G330" s="5" t="n">
+        <v>0.755959</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -18551,22 +18679,20 @@
       <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Share of associates’ loss, net of tax 7</t>
+          <t>Restructuring and other costs (recoveries) 16,20</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" s="5" t="n">
-        <v>0.329652</v>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F331" s="5" t="n">
+        <v>-0.113676</v>
+      </c>
+      <c r="G331" s="5" t="n">
+        <v>0.078333</v>
       </c>
       <c r="H331" t="inlineStr">
         <is>
@@ -18593,24 +18719,18 @@
       <c r="B332" t="inlineStr"/>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Loss before income tax expense</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Loss before following:</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" s="5" t="n">
-        <v>-26.180118</v>
+        <v>-24.497825</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>-23.635963</v>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-23.649134</v>
+      </c>
+      <c r="G332" s="5" t="n">
+        <v>-15.19973</v>
       </c>
       <c r="H332" t="inlineStr">
         <is>
@@ -18637,20 +18757,24 @@
       <c r="B333" t="inlineStr"/>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Income tax (expense) 21 (a)</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
-      <c r="E333" s="5" t="n">
-        <v>-0.249342</v>
+          <t>Other expense 21</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F333" s="5" t="n">
-        <v>-0.164786</v>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.126299</v>
+      </c>
+      <c r="G333" s="5" t="n">
+        <v>0.198791</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
@@ -18674,22 +18798,20 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Net loss attributable to</t>
-        </is>
-      </c>
+      <c r="B334" t="inlineStr"/>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Shareholders of the Company $</t>
+          <t>Change in fair value of convertible loan receivable 6 (b), 8 (ii)</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" s="5" t="n">
-        <v>-26.249234</v>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F334" s="5" t="n">
-        <v>-23.800749</v>
+        <v>-1.842862</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
@@ -18718,33 +18840,25 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Net loss attributable to</t>
-        </is>
-      </c>
+      <c r="B335" t="inlineStr"/>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Non-controlling interests</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
-      <c r="E335" s="5" t="n">
-        <v>0.180226</v>
+          <t>Earn-out shares issued 18 (b)</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G335" s="5" t="n">
+        <v>1.036397</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
@@ -18768,31 +18882,25 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Net loss attributable to</t>
-        </is>
-      </c>
+      <c r="B336" t="inlineStr"/>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E336" s="5" t="n">
-        <v>-26.42946</v>
-      </c>
-      <c r="F336" s="5" t="n">
-        <v>-23.800749</v>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Impairment loss on intangible assets 11</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G336" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
@@ -18816,39 +18924,1105 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B337" t="inlineStr"/>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E337" s="5" t="n">
+        <v>1.136119</v>
+      </c>
+      <c r="F337" s="5" t="n">
+        <v>0.134994</v>
+      </c>
+      <c r="G337" s="5" t="n">
+        <v>-0.01467</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr"/>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Loss from continuing operations before income tax</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F338" s="5" t="n">
+        <v>-22.067565</v>
+      </c>
+      <c r="G338" s="5" t="n">
+        <v>-18.920248</v>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr"/>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Income tax recovery (expense) 22 (a)</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F339" s="5" t="n">
+        <v>-0.163123</v>
+      </c>
+      <c r="G339" s="5" t="n">
+        <v>0.224253</v>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Net loss from continuing operations, net of tax</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F340" s="5" t="n">
+        <v>-22.230688</v>
+      </c>
+      <c r="G340" s="5" t="n">
+        <v>-18.695995</v>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr"/>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Gain on sale of discontinued operations 4</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G341" s="5" t="n">
+        <v>4.096558</v>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr"/>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>(Loss) from discontinued operations 4</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F342" s="5" t="n">
+        <v>-1.570061</v>
+      </c>
+      <c r="G342" s="5" t="n">
+        <v>-0.836062</v>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr"/>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Net income (loss) from discontinued operations</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F343" s="5" t="n">
+        <v>-1.570061</v>
+      </c>
+      <c r="G343" s="5" t="n">
+        <v>3.260496</v>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr"/>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Net (loss) per share (basic and diluted) from continuing</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F344" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="G344" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Net income (loss) per share (basic and diluted) from</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F345" s="5" t="n">
+        <v>-4e-09</v>
+      </c>
+      <c r="G345" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr"/>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Net revenue 4,18</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E346" s="5" t="n">
+        <v>25.104483</v>
+      </c>
+      <c r="F346" s="5" t="n">
+        <v>22.819561</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr"/>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Cost of goods sold 6</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="n">
+        <v>23.014792</v>
+      </c>
+      <c r="F347" s="5" t="n">
+        <v>19.286332</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr"/>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Inventory write-down 6</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" s="5" t="n">
+        <v>-0.6311330000000001</v>
+      </c>
+      <c r="F348" s="5" t="n">
+        <v>-1.85145</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr"/>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization 9,10</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E349" s="5" t="n">
+        <v>2.186433</v>
+      </c>
+      <c r="F349" s="5" t="n">
+        <v>2.043818</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Share-based compensation 17 (d)</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" s="5" t="n">
+        <v>0.772212</v>
+      </c>
+      <c r="F350" s="5" t="n">
+        <v>1.263877</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr"/>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Restructuring and other costs (recoveries) 15,19</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" s="5" t="n">
+        <v>-1.701007</v>
+      </c>
+      <c r="F351" s="5" t="n">
+        <v>-0.113676</v>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr"/>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Other expense (income) 20</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" s="5" t="n">
+        <v>-1.122492</v>
+      </c>
+      <c r="F352" s="5" t="n">
+        <v>0.126772</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr"/>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Change in fair value of convertible loan receivable 22(ii)</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F353" s="5" t="n">
+        <v>-1.842862</v>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Impairment on investment in associates 7</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" s="5" t="n">
+        <v>1.016127</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr"/>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Impairment loss on loans receivable</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" s="5" t="n">
+        <v>0.322887</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr"/>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Share of associates’ loss, net of tax 7</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" s="5" t="n">
+        <v>0.329652</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Loss before income tax expense</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E357" s="5" t="n">
+        <v>-26.180118</v>
+      </c>
+      <c r="F357" s="5" t="n">
+        <v>-23.635963</v>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr"/>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Income tax (expense) 21 (a)</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" s="5" t="n">
+        <v>-0.249342</v>
+      </c>
+      <c r="F358" s="5" t="n">
+        <v>-0.164786</v>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
         <is>
           <t>Net loss attributable to</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Shareholders of the Company $</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" s="5" t="n">
+        <v>-26.249234</v>
+      </c>
+      <c r="F359" s="5" t="n">
+        <v>-23.800749</v>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Net loss attributable to</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E360" s="5" t="n">
+        <v>0.180226</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Net loss attributable to</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E361" s="5" t="n">
+        <v>-26.42946</v>
+      </c>
+      <c r="F361" s="5" t="n">
+        <v>-23.800749</v>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Net loss attributable to</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
         <is>
           <t>Net loss per share (basic and diluted) 17 (e) $</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
-      <c r="E337" s="5" t="n">
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" s="5" t="n">
         <v>-8e-08</v>
       </c>
-      <c r="F337" s="5" t="n">
+      <c r="F362" s="5" t="n">
         <v>-5.999999999999999e-08</v>
       </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J337" t="inlineStr">
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
         <is>
           <t>-</t>
         </is>
